--- a/test/fixtures/xlsx/reference-required-blank/reference-required-blank.xlsx
+++ b/test/fixtures/xlsx/reference-required-blank/reference-required-blank.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t xml:space="preserve">~~table:Target~~</t>
   </si>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Must</t>
   </si>
   <si>
-    <t xml:space="preserve">required, and row 2 leaves it empty</t>
+    <t xml:space="preserve">required, and the rows below say nothing</t>
   </si>
   <si>
     <t xml:space="preserve">foreign</t>
@@ -87,6 +87,15 @@
   </si>
   <si>
     <t xml:space="preserve">y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
   </si>
 </sst>
 </file>
@@ -131,7 +140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K10"/>
+  <dimension ref="B2:K11"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -281,6 +290,17 @@
         <v>24</v>
       </c>
     </row>
+    <row r="11">
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test/fixtures/xlsx/reference-required-blank/reference-required-blank.xlsx
+++ b/test/fixtures/xlsx/reference-required-blank/reference-required-blank.xlsx
@@ -12,78 +12,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
-  <si>
-    <t xml:space="preserve">~~table:Target~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+  <si>
+    <t xml:space="preserve">:table Target</t>
   </si>
   <si>
     <t xml:space="preserve">What the reference below points at.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
+    <t xml:space="preserve">cs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so the row has something in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a third column, so both tables are the same width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A required reference this sheet leaves empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required, and the rows below say nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
   </si>
   <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">cs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">so the row has something in it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a third column, so both tables are the same width</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~~table:Holder~~</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A required reference this sheet leaves empty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must</t>
-  </si>
-  <si>
-    <t xml:space="preserve">required, and the rows below say nothing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
   </si>
   <si>
     <t xml:space="preserve">y</t>
@@ -140,68 +149,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K11"/>
+  <dimension ref="B2:L9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
       </c>
+      <c r="L4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -209,96 +254,62 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
       <c r="I6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K6" t="s">
         <v>9</v>
       </c>
+      <c r="L6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" t="s">
-        <v>6</v>
-      </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>26</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>12</v>
-      </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="I11" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
